--- a/Appraisal Checklist_2025 es-419.xlsx
+++ b/Appraisal Checklist_2025 es-419.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iloprod-my.sharepoint.com/personal/castanedac_ilo_org/Documents/IA EVAL/Streamlit/resultados_rubricas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ageidv/ilo/deploy_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{2F4D44E3-2D73-4CE6-A5EF-DF0E183D1022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF0F81B-8AA3-4318-A753-FB998EA4F3E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C734FCD9-2587-6442-9259-B67DECA390AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introducción" sheetId="3" r:id="rId1"/>
     <sheet name="Lista de verificación" sheetId="1" r:id="rId2"/>
     <sheet name="Lista 2025 actualizada" sheetId="5" r:id="rId3"/>
     <sheet name="PUNTUACIÓN DE EVALUACIÓN" sheetId="4" r:id="rId4"/>
+    <sheet name="rubric" sheetId="6" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">[1]Checklist!$A$1:$H$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">[1]Checklist!$A$1:$H$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -160,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="219">
   <si>
     <t>Preguntas de evaluación</t>
   </si>
@@ -1177,12 +1179,237 @@
       <t xml:space="preserve"> explica de manera clara la ventaja comparativa de la OIT para llevar a cabo el proyecto, presenta experiencias previas, lecciones aprendidas de evaluaciones pertinentes (evaluaciones de proyectos, programas por país o estrategias,véase www.ilo.org/ievaldiscovery) y explica cómo estas han influido en la estrategia del proyecto.? </t>
     </r>
   </si>
+  <si>
+    <t>1.2.1</t>
+  </si>
+  <si>
+    <t>1.2.3</t>
+  </si>
+  <si>
+    <t>1.2.2</t>
+  </si>
+  <si>
+    <t>1.3.1</t>
+  </si>
+  <si>
+    <t>1.3.2</t>
+  </si>
+  <si>
+    <t>1.3.3</t>
+  </si>
+  <si>
+    <t>1.3.4</t>
+  </si>
+  <si>
+    <t>1.3.5</t>
+  </si>
+  <si>
+    <t>1.4.1</t>
+  </si>
+  <si>
+    <t>1.4.2</t>
+  </si>
+  <si>
+    <t>1.4.3</t>
+  </si>
+  <si>
+    <t>1.5.1</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
+    <t>1.5.4</t>
+  </si>
+  <si>
+    <t>1.5.5</t>
+  </si>
+  <si>
+    <t>1.5.6</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>2.1.3</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+  <si>
+    <t>2.2.2</t>
+  </si>
+  <si>
+    <t>2.2.3</t>
+  </si>
+  <si>
+    <t>2.3.1</t>
+  </si>
+  <si>
+    <t>2.3.2</t>
+  </si>
+  <si>
+    <t>2.4.1</t>
+  </si>
+  <si>
+    <t>2.4.2</t>
+  </si>
+  <si>
+    <t>2.4.3</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
+  </si>
+  <si>
+    <t>2.4.5</t>
+  </si>
+  <si>
+    <t>3.1.1</t>
+  </si>
+  <si>
+    <t>3.1.2</t>
+  </si>
+  <si>
+    <t>3.1.3</t>
+  </si>
+  <si>
+    <t>3.1.4</t>
+  </si>
+  <si>
+    <t>3.1.5</t>
+  </si>
+  <si>
+    <t>3.2.1</t>
+  </si>
+  <si>
+    <t>3.2.2</t>
+  </si>
+  <si>
+    <t>3.2.3</t>
+  </si>
+  <si>
+    <t>3.3.1</t>
+  </si>
+  <si>
+    <t>3.3.2</t>
+  </si>
+  <si>
+    <t>3.4.1</t>
+  </si>
+  <si>
+    <t>3.4.2</t>
+  </si>
+  <si>
+    <t>3.4.3</t>
+  </si>
+  <si>
+    <t>3.4.4</t>
+  </si>
+  <si>
+    <t>3.4.5</t>
+  </si>
+  <si>
+    <t>3.4.6</t>
+  </si>
+  <si>
+    <t>3.4.7</t>
+  </si>
+  <si>
+    <t>3.5.1</t>
+  </si>
+  <si>
+    <t>3.5.2</t>
+  </si>
+  <si>
+    <t>3.5.3</t>
+  </si>
+  <si>
+    <t>3.5.4</t>
+  </si>
+  <si>
+    <t>3.5.5</t>
+  </si>
+  <si>
+    <t>3.6.1</t>
+  </si>
+  <si>
+    <t>3.6.2</t>
+  </si>
+  <si>
+    <t>3.6.3</t>
+  </si>
+  <si>
+    <t>3.7.1</t>
+  </si>
+  <si>
+    <t>3.7.2</t>
+  </si>
+  <si>
+    <t>4.1.1</t>
+  </si>
+  <si>
+    <t>4.1.2</t>
+  </si>
+  <si>
+    <t>4.1.3</t>
+  </si>
+  <si>
+    <t>4.1.4</t>
+  </si>
+  <si>
+    <t>4.1.5</t>
+  </si>
+  <si>
+    <t>4.2.1</t>
+  </si>
+  <si>
+    <t>4.2.2</t>
+  </si>
+  <si>
+    <t>4.2.3</t>
+  </si>
+  <si>
+    <t>4.2.4</t>
+  </si>
+  <si>
+    <t>4.2.5</t>
+  </si>
+  <si>
+    <t>4.3.1</t>
+  </si>
+  <si>
+    <t>4.4.1</t>
+  </si>
+  <si>
+    <t>4.4.2</t>
+  </si>
+  <si>
+    <t>4.4.3</t>
+  </si>
+  <si>
+    <t>5.1.1</t>
+  </si>
+  <si>
+    <t>5.2.1</t>
+  </si>
+  <si>
+    <t>1.2 ¿Iyntifica con cooperación ODS pertindetes, con de ár cooperación ár las Naciones Unidas, que des responsable ár que ODS y otros marcos ár cooperación, incluidos los planes nacionales de desarrollo, y se ajusta N conque?</t>
+  </si>
+  <si>
+    <t>1.2 ¿Isonntifica indicadores ODS pertinlostes, indicadores que in cooperación in las Naciones Unidas, vinculados ques los in vinculados ODS y otros marcos in cooperación, incluidos los planes nacionales de desarrollo, y se ajusta c indicadoresvinculados?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1312,6 +1539,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1393,7 +1626,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1942,12 +2175,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2041,6 +2325,301 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2068,24 +2647,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2116,9 +2677,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2131,36 +2689,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2173,246 +2701,53 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2562,6 +2897,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2592,6 +2937,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2612,6 +2977,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2622,6 +2997,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2632,6 +3017,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2652,6 +3057,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2662,6 +3087,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2672,6 +3117,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2682,6 +3137,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2702,6 +3167,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2712,6 +3207,176 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2722,6 +3387,76 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2742,6 +3477,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2752,6 +3547,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2762,6 +3567,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2782,6 +3607,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2802,6 +3637,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2822,6 +3687,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2832,6 +3707,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2842,6 +3737,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2852,6 +3767,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2882,6 +3837,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2942,6 +3907,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2962,6 +3937,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2982,661 +3967,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5346,10 +5681,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5367,94 +5702,94 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="4" max="4" width="63.5703125" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" customWidth="1"/>
-    <col min="8" max="8" width="35.42578125" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="38.5" customWidth="1"/>
+    <col min="4" max="4" width="63.5" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" customWidth="1"/>
+    <col min="8" max="8" width="35.5" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="151" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="59"/>
+    <row r="2" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="142"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="151"/>
       <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="59"/>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="143"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="151"/>
       <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="53"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="57"/>
-    </row>
-    <row r="6" spans="1:9" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="146"/>
+    </row>
+    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="147"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="150"/>
+    </row>
+    <row r="6" spans="1:9" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
@@ -5467,13 +5802,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
-      <c r="B7" s="145" t="s">
+    <row r="7" spans="1:9" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="68"/>
+      <c r="B7" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="147"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="45"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
@@ -5486,13 +5821,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44"/>
-      <c r="B8" s="33" t="s">
+    <row r="8" spans="1:9" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="107"/>
+      <c r="B8" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="35"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="134"/>
       <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
@@ -5505,30 +5840,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="63" t="s">
+    <row r="9" spans="1:9" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="66"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="9" t="s">
         <v>11</v>
       </c>
@@ -5543,13 +5878,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="B11" s="71" t="s">
+    <row r="11" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="68"/>
+      <c r="B11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
       <c r="E11" s="10" t="s">
         <v>11</v>
       </c>
@@ -5564,13 +5899,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44"/>
-      <c r="B12" s="72" t="s">
+    <row r="12" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="107"/>
+      <c r="B12" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="11" t="s">
         <v>11</v>
       </c>
@@ -5585,30 +5920,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="63" t="s">
+    <row r="13" spans="1:9" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="66"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
+    <row r="14" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="9" t="s">
         <v>11</v>
       </c>
@@ -5621,13 +5956,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="68"/>
-      <c r="B15" s="71" t="s">
+    <row r="15" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="61"/>
+      <c r="B15" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="10" t="s">
         <v>11</v>
       </c>
@@ -5638,13 +5973,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68"/>
-      <c r="B16" s="79" t="s">
+    <row r="16" spans="1:9" ht="60.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="61"/>
+      <c r="B16" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
       <c r="E16" s="10" t="s">
         <v>11</v>
       </c>
@@ -5657,13 +5992,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="71" t="s">
+    <row r="17" spans="1:9" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="61"/>
+      <c r="B17" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="10" t="s">
         <v>11</v>
       </c>
@@ -5676,13 +6011,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="80" t="s">
+    <row r="18" spans="1:9" ht="56.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="62"/>
+      <c r="B18" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="11" t="s">
         <v>11</v>
       </c>
@@ -5693,30 +6028,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
+    <row r="19" spans="1:9" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="66"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67" t="s">
+    <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="9" t="s">
         <v>11</v>
       </c>
@@ -5727,13 +6062,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="71" t="s">
+    <row r="21" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="61"/>
+      <c r="B21" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
       <c r="E21" s="10" t="s">
         <v>11</v>
       </c>
@@ -5744,13 +6079,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="99" t="s">
+    <row r="22" spans="1:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="62"/>
+      <c r="B22" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
       <c r="E22" s="11" t="s">
         <v>14</v>
       </c>
@@ -5761,30 +6096,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="63" t="s">
+    <row r="23" spans="1:9" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="66"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
       <c r="I23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="68" t="s">
+    <row r="24" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
       <c r="E24" s="9" t="s">
         <v>14</v>
       </c>
@@ -5795,13 +6130,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68"/>
-      <c r="B25" s="97" t="s">
+    <row r="25" spans="1:9" ht="84.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="61"/>
+      <c r="B25" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="10" t="s">
         <v>11</v>
       </c>
@@ -5812,13 +6147,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68"/>
-      <c r="B26" s="100" t="s">
+    <row r="26" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="61"/>
+      <c r="B26" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="102"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="113"/>
       <c r="E26" s="10" t="s">
         <v>11</v>
       </c>
@@ -5829,13 +6164,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68"/>
-      <c r="B27" s="100" t="s">
+    <row r="27" spans="1:9" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="61"/>
+      <c r="B27" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="101"/>
-      <c r="D27" s="102"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="113"/>
       <c r="E27" s="10" t="s">
         <v>11</v>
       </c>
@@ -5846,13 +6181,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="88.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68"/>
-      <c r="B28" s="98" t="s">
+    <row r="28" spans="1:9" ht="89" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="61"/>
+      <c r="B28" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
       <c r="E28" s="10" t="s">
         <v>14</v>
       </c>
@@ -5863,13 +6198,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="69"/>
-      <c r="B29" s="72" t="s">
+    <row r="29" spans="1:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="62"/>
+      <c r="B29" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
       <c r="E29" s="11" t="s">
         <v>14</v>
       </c>
@@ -5882,71 +6217,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="81" t="s">
+    <row r="30" spans="1:9" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
       <c r="I30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="51" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="73"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="155"/>
       <c r="I31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="74"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="75"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="156"/>
+      <c r="B32" s="149"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="157"/>
       <c r="I32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="76"/>
+    <row r="33" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="147"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="158"/>
       <c r="I33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+    <row r="34" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="9" t="s">
         <v>14</v>
       </c>
@@ -5957,13 +6292,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="68"/>
-      <c r="B35" s="71" t="s">
+    <row r="35" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="61"/>
+      <c r="B35" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
       <c r="E35" s="10" t="s">
         <v>11</v>
       </c>
@@ -5974,13 +6309,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="69"/>
-      <c r="B36" s="72" t="s">
+    <row r="36" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="62"/>
+      <c r="B36" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
       <c r="E36" s="11" t="s">
         <v>11</v>
       </c>
@@ -5991,30 +6326,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="63" t="s">
+    <row r="37" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="66"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
       <c r="I37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67" t="s">
+    <row r="38" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
       <c r="E38" s="9" t="s">
         <v>14</v>
       </c>
@@ -6025,13 +6360,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="68"/>
-      <c r="B39" s="71" t="s">
+    <row r="39" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="61"/>
+      <c r="B39" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
       <c r="E39" s="10" t="s">
         <v>11</v>
       </c>
@@ -6042,13 +6377,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="69"/>
-      <c r="B40" s="72" t="s">
+    <row r="40" spans="1:9" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="62"/>
+      <c r="B40" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
       <c r="E40" s="11" t="s">
         <v>11</v>
       </c>
@@ -6059,107 +6394,107 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="63" t="s">
+    <row r="41" spans="1:9" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="64"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="66"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="48"/>
       <c r="I41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+    <row r="42" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="84" t="s">
+      <c r="B42" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="88" t="s">
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="141"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="92"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="128"/>
       <c r="I42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="93"/>
+    <row r="43" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="61"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="153"/>
+      <c r="H43" s="129"/>
       <c r="I43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="68"/>
-      <c r="B44" s="86" t="s">
+    <row r="44" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="61"/>
+      <c r="B44" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="90" t="s">
+      <c r="C44" s="122"/>
+      <c r="D44" s="122"/>
+      <c r="E44" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="F44" s="143"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="94"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="153"/>
+      <c r="H44" s="130"/>
       <c r="I44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="94.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="68"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="87"/>
-      <c r="D45" s="87"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="95"/>
+    <row r="45" spans="1:9" ht="94.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="61"/>
+      <c r="B45" s="123"/>
+      <c r="C45" s="123"/>
+      <c r="D45" s="123"/>
+      <c r="E45" s="127"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="154"/>
+      <c r="H45" s="131"/>
       <c r="I45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="63" t="s">
+    <row r="46" spans="1:9" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="66"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="48"/>
       <c r="I46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
+    <row r="47" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="70" t="s">
+      <c r="B47" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
       <c r="E47" s="9" t="s">
         <v>11</v>
       </c>
@@ -6170,13 +6505,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="68"/>
-      <c r="B48" s="71" t="s">
+    <row r="48" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="61"/>
+      <c r="B48" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
       <c r="E48" s="10" t="s">
         <v>11</v>
       </c>
@@ -6187,13 +6522,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="68"/>
-      <c r="B49" s="71" t="s">
+    <row r="49" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="61"/>
+      <c r="B49" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="71"/>
-      <c r="D49" s="71"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
       <c r="E49" s="10" t="s">
         <v>11</v>
       </c>
@@ -6204,13 +6539,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="68"/>
-      <c r="B50" s="71" t="s">
+    <row r="50" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="61"/>
+      <c r="B50" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="71"/>
-      <c r="D50" s="71"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
       <c r="E50" s="10" t="s">
         <v>11</v>
       </c>
@@ -6221,13 +6556,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="72" t="s">
+    <row r="51" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="62"/>
+      <c r="B51" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
       <c r="E51" s="11" t="s">
         <v>11</v>
       </c>
@@ -6238,58 +6573,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="63" t="s">
+    <row r="52" spans="1:9" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="64"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="64"/>
-      <c r="H52" s="66"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="48"/>
       <c r="I52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="110" t="s">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="111"/>
-      <c r="C53" s="111"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="111"/>
-      <c r="F53" s="111"/>
-      <c r="G53" s="111"/>
-      <c r="H53" s="112"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="75"/>
       <c r="I53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="113"/>
-      <c r="B54" s="114"/>
-      <c r="C54" s="114"/>
-      <c r="D54" s="114"/>
-      <c r="E54" s="114"/>
-      <c r="F54" s="115"/>
-      <c r="G54" s="114"/>
-      <c r="H54" s="116"/>
+    <row r="54" spans="1:9" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="79"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="81"/>
       <c r="I54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="103" t="s">
+    <row r="55" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="70" t="s">
+      <c r="B55" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="9" t="s">
         <v>11</v>
       </c>
@@ -6302,13 +6637,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="104"/>
-      <c r="B56" s="71" t="s">
+    <row r="56" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="101"/>
+      <c r="B56" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
       <c r="E56" s="10" t="s">
         <v>11</v>
       </c>
@@ -6321,13 +6656,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="104"/>
-      <c r="B57" s="117" t="s">
+    <row r="57" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="101"/>
+      <c r="B57" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="117"/>
-      <c r="D57" s="117"/>
+      <c r="C57" s="105"/>
+      <c r="D57" s="105"/>
       <c r="E57" s="10" t="s">
         <v>11</v>
       </c>
@@ -6340,13 +6675,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="104"/>
-      <c r="B58" s="71" t="s">
+    <row r="58" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="101"/>
+      <c r="B58" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="71"/>
-      <c r="D58" s="71"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
       <c r="E58" s="10" t="s">
         <v>11</v>
       </c>
@@ -6359,13 +6694,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="105"/>
-      <c r="B59" s="72" t="s">
+    <row r="59" spans="1:9" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="72"/>
+      <c r="B59" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="72"/>
-      <c r="D59" s="72"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
       <c r="E59" s="11" t="s">
         <v>14</v>
       </c>
@@ -6378,30 +6713,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="84.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="63" t="s">
+    <row r="60" spans="1:9" ht="84.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="64"/>
-      <c r="C60" s="64"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="66"/>
+      <c r="B60" s="47"/>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="48"/>
       <c r="I60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="103" t="s">
+    <row r="61" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="106" t="s">
+      <c r="B61" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="C61" s="106"/>
-      <c r="D61" s="106"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="102"/>
       <c r="E61" s="9" t="s">
         <v>11</v>
       </c>
@@ -6412,13 +6747,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="104"/>
-      <c r="B62" s="71" t="s">
+    <row r="62" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="101"/>
+      <c r="B62" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
+      <c r="C62" s="50"/>
+      <c r="D62" s="50"/>
       <c r="E62" s="10" t="s">
         <v>11</v>
       </c>
@@ -6431,13 +6766,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="105"/>
-      <c r="B63" s="72" t="s">
+    <row r="63" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="72"/>
+      <c r="B63" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="72"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
       <c r="E63" s="11" t="s">
         <v>11</v>
       </c>
@@ -6448,30 +6783,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="107" t="s">
+    <row r="64" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="B64" s="108"/>
-      <c r="C64" s="108"/>
-      <c r="D64" s="108"/>
-      <c r="E64" s="108"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="108"/>
-      <c r="H64" s="109"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="104"/>
       <c r="I64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="125" t="s">
+    <row r="65" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="70" t="s">
+      <c r="B65" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C65" s="70"/>
-      <c r="D65" s="70"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
       <c r="E65" s="9" t="s">
         <v>14</v>
       </c>
@@ -6482,13 +6817,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="126"/>
-      <c r="B66" s="124" t="s">
+    <row r="66" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="53"/>
+      <c r="B66" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="124"/>
-      <c r="D66" s="124"/>
+      <c r="C66" s="97"/>
+      <c r="D66" s="97"/>
       <c r="E66" s="10" t="s">
         <v>14</v>
       </c>
@@ -6499,30 +6834,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="118" t="s">
+    <row r="67" spans="1:9" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="B67" s="83"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="83"/>
-      <c r="F67" s="65"/>
-      <c r="G67" s="83"/>
-      <c r="H67" s="119"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="92"/>
       <c r="I67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="120" t="s">
+    <row r="68" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="70" t="s">
+      <c r="B68" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="70"/>
-      <c r="D68" s="70"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
       <c r="E68" s="9" t="s">
         <v>11</v>
       </c>
@@ -6533,13 +6868,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="56.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="121"/>
-      <c r="B69" s="127" t="s">
+    <row r="69" spans="1:9" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="94"/>
+      <c r="B69" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="C69" s="128"/>
-      <c r="D69" s="129"/>
+      <c r="C69" s="99"/>
+      <c r="D69" s="100"/>
       <c r="E69" s="25" t="s">
         <v>14</v>
       </c>
@@ -6550,13 +6885,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="121"/>
-      <c r="B70" s="127" t="s">
+    <row r="70" spans="1:9" ht="50.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="94"/>
+      <c r="B70" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="128"/>
-      <c r="D70" s="129"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="100"/>
       <c r="E70" s="25" t="s">
         <v>14</v>
       </c>
@@ -6567,13 +6902,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="121"/>
-      <c r="B71" s="127" t="s">
+    <row r="71" spans="1:9" ht="34.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="94"/>
+      <c r="B71" s="98" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="128"/>
-      <c r="D71" s="129"/>
+      <c r="C71" s="99"/>
+      <c r="D71" s="100"/>
       <c r="E71" s="25" t="s">
         <v>14</v>
       </c>
@@ -6584,13 +6919,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="122"/>
-      <c r="B72" s="71" t="s">
+    <row r="72" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="95"/>
+      <c r="B72" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="71"/>
-      <c r="D72" s="71"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
       <c r="E72" s="10"/>
       <c r="F72" s="24"/>
       <c r="G72" s="10"/>
@@ -6599,13 +6934,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="122"/>
-      <c r="B73" s="71" t="s">
+    <row r="73" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="95"/>
+      <c r="B73" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="71"/>
-      <c r="D73" s="71"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
       <c r="E73" s="10" t="s">
         <v>11</v>
       </c>
@@ -6616,13 +6951,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="123"/>
-      <c r="B74" s="72" t="s">
+    <row r="74" spans="1:9" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="96"/>
+      <c r="B74" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="C74" s="72"/>
-      <c r="D74" s="72"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="69"/>
       <c r="E74" s="11" t="s">
         <v>11</v>
       </c>
@@ -6633,30 +6968,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="63" t="s">
+    <row r="75" spans="1:9" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="64"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="66"/>
+      <c r="B75" s="47"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="47"/>
+      <c r="H75" s="48"/>
       <c r="I75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="125" t="s">
+    <row r="76" spans="1:9" ht="88.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="131" t="s">
+      <c r="B76" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C76" s="131"/>
-      <c r="D76" s="131"/>
+      <c r="C76" s="83"/>
+      <c r="D76" s="83"/>
       <c r="E76" s="9"/>
       <c r="F76" s="24"/>
       <c r="G76" s="10"/>
@@ -6667,13 +7002,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="126"/>
-      <c r="B77" s="97" t="s">
+    <row r="77" spans="1:9" ht="64.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="53"/>
+      <c r="B77" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="97"/>
-      <c r="D77" s="97"/>
+      <c r="C77" s="89"/>
+      <c r="D77" s="89"/>
       <c r="E77" s="10"/>
       <c r="F77" s="24"/>
       <c r="G77" s="10"/>
@@ -6684,13 +7019,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="126"/>
-      <c r="B78" s="132" t="s">
+    <row r="78" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="53"/>
+      <c r="B78" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="132"/>
-      <c r="D78" s="132"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="90"/>
       <c r="E78" s="10"/>
       <c r="F78" s="24"/>
       <c r="G78" s="10"/>
@@ -6701,13 +7036,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="126"/>
-      <c r="B79" s="71" t="s">
+    <row r="79" spans="1:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="53"/>
+      <c r="B79" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
       <c r="E79" s="10"/>
       <c r="F79" s="24"/>
       <c r="G79" s="10"/>
@@ -6718,13 +7053,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="259.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="150"/>
-      <c r="B80" s="148" t="s">
+    <row r="80" spans="1:9" ht="260" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="54"/>
+      <c r="B80" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="C80" s="148"/>
-      <c r="D80" s="148"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
       <c r="E80" s="11"/>
       <c r="F80" s="24"/>
       <c r="G80" s="10"/>
@@ -6735,30 +7070,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="63" t="s">
+    <row r="81" spans="1:9" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="64"/>
-      <c r="C81" s="64"/>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="66"/>
+      <c r="B81" s="47"/>
+      <c r="C81" s="47"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="47"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="47"/>
+      <c r="H81" s="48"/>
       <c r="I81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="39" t="s">
+    <row r="82" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="B82" s="130" t="s">
+      <c r="B82" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C82" s="130"/>
-      <c r="D82" s="130"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="88"/>
       <c r="E82" s="9" t="s">
         <v>11</v>
       </c>
@@ -6769,13 +7104,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="40"/>
-      <c r="B83" s="97" t="s">
+    <row r="83" spans="1:9" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="139"/>
+      <c r="B83" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C83" s="97"/>
-      <c r="D83" s="97"/>
+      <c r="C83" s="89"/>
+      <c r="D83" s="89"/>
       <c r="E83" s="11" t="s">
         <v>11</v>
       </c>
@@ -6786,13 +7121,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="41"/>
-      <c r="B84" s="36" t="s">
+    <row r="84" spans="1:9" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="140"/>
+      <c r="B84" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="C84" s="37"/>
-      <c r="D84" s="38"/>
+      <c r="C84" s="136"/>
+      <c r="D84" s="137"/>
       <c r="E84" s="17" t="s">
         <v>11</v>
       </c>
@@ -6803,30 +7138,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="63" t="s">
+    <row r="85" spans="1:9" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="64"/>
-      <c r="C85" s="64"/>
-      <c r="D85" s="64"/>
-      <c r="E85" s="64"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="64"/>
-      <c r="H85" s="66"/>
+      <c r="B85" s="47"/>
+      <c r="C85" s="47"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="47"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="47"/>
+      <c r="H85" s="48"/>
       <c r="I85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="103" t="s">
+    <row r="86" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="70" t="s">
+      <c r="B86" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="C86" s="70"/>
-      <c r="D86" s="70"/>
+      <c r="C86" s="63"/>
+      <c r="D86" s="63"/>
       <c r="E86" s="9" t="s">
         <v>11</v>
       </c>
@@ -6837,13 +7172,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="105"/>
-      <c r="B87" s="72" t="s">
+    <row r="87" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="72"/>
+      <c r="B87" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="C87" s="72"/>
-      <c r="D87" s="72"/>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
       <c r="E87" s="11" t="s">
         <v>11</v>
       </c>
@@ -6854,71 +7189,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="63" t="s">
+    <row r="88" spans="1:9" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B88" s="64"/>
-      <c r="C88" s="64"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
-      <c r="F88" s="83"/>
-      <c r="G88" s="64"/>
-      <c r="H88" s="66"/>
+      <c r="B88" s="47"/>
+      <c r="C88" s="47"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="47"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="47"/>
+      <c r="H88" s="48"/>
       <c r="I88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="110" t="s">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="B89" s="111"/>
-      <c r="C89" s="111"/>
-      <c r="D89" s="111"/>
-      <c r="E89" s="111"/>
-      <c r="F89" s="111"/>
-      <c r="G89" s="111"/>
-      <c r="H89" s="112"/>
+      <c r="B89" s="74"/>
+      <c r="C89" s="74"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="74"/>
+      <c r="H89" s="75"/>
       <c r="I89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="134"/>
-      <c r="B90" s="115"/>
-      <c r="C90" s="115"/>
-      <c r="D90" s="115"/>
-      <c r="E90" s="115"/>
-      <c r="F90" s="115"/>
-      <c r="G90" s="115"/>
-      <c r="H90" s="135"/>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="76"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="77"/>
+      <c r="E90" s="77"/>
+      <c r="F90" s="77"/>
+      <c r="G90" s="77"/>
+      <c r="H90" s="78"/>
       <c r="I90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="113"/>
-      <c r="B91" s="114"/>
-      <c r="C91" s="114"/>
-      <c r="D91" s="114"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="115"/>
-      <c r="G91" s="114"/>
-      <c r="H91" s="116"/>
+    <row r="91" spans="1:9" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="79"/>
+      <c r="B91" s="80"/>
+      <c r="C91" s="80"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="77"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="81"/>
       <c r="I91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="67" t="s">
+    <row r="92" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="131" t="s">
+      <c r="B92" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="C92" s="131"/>
-      <c r="D92" s="131"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="9" t="s">
         <v>11</v>
       </c>
@@ -6929,13 +7264,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="68"/>
-      <c r="B93" s="71" t="s">
+    <row r="93" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="61"/>
+      <c r="B93" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="C93" s="71"/>
-      <c r="D93" s="71"/>
+      <c r="C93" s="50"/>
+      <c r="D93" s="50"/>
       <c r="E93" s="10" t="s">
         <v>11</v>
       </c>
@@ -6946,13 +7281,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="68"/>
-      <c r="B94" s="71" t="s">
+    <row r="94" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="61"/>
+      <c r="B94" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C94" s="71"/>
-      <c r="D94" s="71"/>
+      <c r="C94" s="50"/>
+      <c r="D94" s="50"/>
       <c r="E94" s="10" t="s">
         <v>11</v>
       </c>
@@ -6963,13 +7298,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="136"/>
-      <c r="B95" s="138" t="s">
+    <row r="95" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="82"/>
+      <c r="B95" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="C95" s="139"/>
-      <c r="D95" s="140"/>
+      <c r="C95" s="86"/>
+      <c r="D95" s="87"/>
       <c r="E95" s="26" t="s">
         <v>11</v>
       </c>
@@ -6980,13 +7315,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="69"/>
-      <c r="B96" s="137" t="s">
+    <row r="96" spans="1:9" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="62"/>
+      <c r="B96" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="C96" s="137"/>
-      <c r="D96" s="137"/>
+      <c r="C96" s="84"/>
+      <c r="D96" s="84"/>
       <c r="E96" s="11"/>
       <c r="F96" s="24"/>
       <c r="G96" s="10"/>
@@ -6995,30 +7330,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="63" t="s">
+    <row r="97" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B97" s="64"/>
-      <c r="C97" s="64"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="64"/>
-      <c r="F97" s="65"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="66"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="48"/>
       <c r="I97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="67" t="s">
+    <row r="98" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B98" s="70" t="s">
+      <c r="B98" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
+      <c r="C98" s="63"/>
+      <c r="D98" s="63"/>
       <c r="E98" s="9" t="s">
         <v>11</v>
       </c>
@@ -7029,13 +7364,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="43"/>
-      <c r="B99" s="71" t="s">
+    <row r="99" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="68"/>
+      <c r="B99" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
+      <c r="C99" s="50"/>
+      <c r="D99" s="50"/>
       <c r="E99" s="10" t="s">
         <v>14</v>
       </c>
@@ -7046,13 +7381,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="43"/>
-      <c r="B100" s="149" t="s">
+    <row r="100" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="68"/>
+      <c r="B100" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="C100" s="149"/>
-      <c r="D100" s="149"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
       <c r="E100" s="10" t="s">
         <v>14</v>
       </c>
@@ -7063,13 +7398,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="43"/>
-      <c r="B101" s="71" t="s">
+    <row r="101" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="68"/>
+      <c r="B101" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="C101" s="71"/>
-      <c r="D101" s="71"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
       <c r="E101" s="10" t="s">
         <v>14</v>
       </c>
@@ -7080,13 +7415,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="69"/>
-      <c r="B102" s="72" t="s">
+    <row r="102" spans="1:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="62"/>
+      <c r="B102" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
+      <c r="C102" s="69"/>
+      <c r="D102" s="69"/>
       <c r="E102" s="11" t="s">
         <v>14</v>
       </c>
@@ -7097,30 +7432,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="63" t="s">
+    <row r="103" spans="1:9" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B103" s="64"/>
-      <c r="C103" s="64"/>
-      <c r="D103" s="64"/>
-      <c r="E103" s="64"/>
-      <c r="F103" s="83"/>
-      <c r="G103" s="64"/>
-      <c r="H103" s="66"/>
+      <c r="B103" s="47"/>
+      <c r="C103" s="47"/>
+      <c r="D103" s="47"/>
+      <c r="E103" s="47"/>
+      <c r="F103" s="66"/>
+      <c r="G103" s="47"/>
+      <c r="H103" s="48"/>
       <c r="I103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B104" s="133" t="s">
+      <c r="B104" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="C104" s="133"/>
-      <c r="D104" s="133"/>
+      <c r="C104" s="70"/>
+      <c r="D104" s="70"/>
       <c r="E104" s="6" t="s">
         <v>14</v>
       </c>
@@ -7132,30 +7467,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="63" t="s">
+    <row r="105" spans="1:9" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B105" s="64"/>
-      <c r="C105" s="64"/>
-      <c r="D105" s="64"/>
-      <c r="E105" s="64"/>
-      <c r="F105" s="108"/>
-      <c r="G105" s="64"/>
-      <c r="H105" s="66"/>
+      <c r="B105" s="47"/>
+      <c r="C105" s="47"/>
+      <c r="D105" s="47"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="59"/>
+      <c r="G105" s="47"/>
+      <c r="H105" s="48"/>
       <c r="I105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="67" t="s">
+    <row r="106" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="B106" s="70" t="s">
+      <c r="B106" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="C106" s="70"/>
-      <c r="D106" s="70"/>
+      <c r="C106" s="63"/>
+      <c r="D106" s="63"/>
       <c r="E106" s="9" t="s">
         <v>14</v>
       </c>
@@ -7166,13 +7501,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="68"/>
-      <c r="B107" s="154" t="s">
+    <row r="107" spans="1:9" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="61"/>
+      <c r="B107" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="C107" s="154"/>
-      <c r="D107" s="154"/>
+      <c r="C107" s="64"/>
+      <c r="D107" s="64"/>
       <c r="E107" s="10" t="s">
         <v>14</v>
       </c>
@@ -7183,13 +7518,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="69"/>
-      <c r="B108" s="155" t="s">
+    <row r="108" spans="1:9" ht="105.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="62"/>
+      <c r="B108" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="C108" s="155"/>
-      <c r="D108" s="155"/>
+      <c r="C108" s="65"/>
+      <c r="D108" s="65"/>
       <c r="E108" s="11"/>
       <c r="F108" s="24"/>
       <c r="G108" s="10"/>
@@ -7198,45 +7533,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="63" t="s">
+    <row r="109" spans="1:9" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B109" s="64"/>
-      <c r="C109" s="64"/>
-      <c r="D109" s="64"/>
-      <c r="E109" s="64"/>
-      <c r="F109" s="83"/>
-      <c r="G109" s="64"/>
-      <c r="H109" s="66"/>
+      <c r="B109" s="47"/>
+      <c r="C109" s="47"/>
+      <c r="D109" s="47"/>
+      <c r="E109" s="47"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="47"/>
+      <c r="H109" s="48"/>
       <c r="I109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="151" t="s">
+    <row r="110" spans="1:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="B110" s="152"/>
-      <c r="C110" s="152"/>
-      <c r="D110" s="152"/>
-      <c r="E110" s="152"/>
-      <c r="F110" s="152"/>
-      <c r="G110" s="152"/>
-      <c r="H110" s="153"/>
+      <c r="B110" s="57"/>
+      <c r="C110" s="57"/>
+      <c r="D110" s="57"/>
+      <c r="E110" s="57"/>
+      <c r="F110" s="57"/>
+      <c r="G110" s="57"/>
+      <c r="H110" s="58"/>
       <c r="I110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B111" s="58" t="s">
+      <c r="B111" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="C111" s="58"/>
-      <c r="D111" s="58"/>
+      <c r="C111" s="55"/>
+      <c r="D111" s="55"/>
       <c r="E111" s="6" t="s">
         <v>11</v>
       </c>
@@ -7246,30 +7581,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="63" t="s">
+    <row r="112" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B112" s="64"/>
-      <c r="C112" s="64"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="66"/>
+      <c r="B112" s="47"/>
+      <c r="C112" s="47"/>
+      <c r="D112" s="47"/>
+      <c r="E112" s="47"/>
+      <c r="F112" s="47"/>
+      <c r="G112" s="47"/>
+      <c r="H112" s="48"/>
       <c r="I112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B113" s="58" t="s">
+      <c r="B113" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
+      <c r="C113" s="55"/>
+      <c r="D113" s="55"/>
       <c r="E113" s="6" t="s">
         <v>11</v>
       </c>
@@ -7279,28 +7614,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="63" t="s">
+    <row r="114" spans="1:9" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B114" s="64"/>
-      <c r="C114" s="64"/>
-      <c r="D114" s="64"/>
-      <c r="E114" s="64"/>
-      <c r="F114" s="64"/>
-      <c r="G114" s="64"/>
-      <c r="H114" s="66"/>
-    </row>
-    <row r="115" spans="1:9" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="77" t="s">
+      <c r="B114" s="47"/>
+      <c r="C114" s="47"/>
+      <c r="D114" s="47"/>
+      <c r="E114" s="47"/>
+      <c r="F114" s="47"/>
+      <c r="G114" s="47"/>
+      <c r="H114" s="48"/>
+    </row>
+    <row r="115" spans="1:9" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="B115" s="78"/>
-      <c r="C115" s="78"/>
-      <c r="D115" s="78"/>
-      <c r="E115" s="78"/>
-      <c r="F115" s="78"/>
-      <c r="G115" s="78"/>
+      <c r="B115" s="115"/>
+      <c r="C115" s="115"/>
+      <c r="D115" s="115"/>
+      <c r="E115" s="115"/>
+      <c r="F115" s="115"/>
+      <c r="G115" s="115"/>
       <c r="H115" s="23" t="e">
         <f>AVERAGE(H6,H10:H12,H14,H16:H17,H29,H55:H59,H62,H76:H80,H104)</f>
         <v>#DIV/0!</v>
@@ -7309,9 +7644,121 @@
         <v>76</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:H5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A31:H33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="B42:D43"/>
+    <mergeCell ref="B44:D45"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A53:H54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:A74"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A89:H91"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B95:D95"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="F42:F43"/>
     <mergeCell ref="F44:F45"/>
@@ -7336,118 +7783,6 @@
     <mergeCell ref="A98:A102"/>
     <mergeCell ref="B98:D98"/>
     <mergeCell ref="B102:D102"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A89:H91"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A53:H54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A115:G115"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="B42:D43"/>
-    <mergeCell ref="B44:D45"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:H5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G1:G3"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A31:H33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:F1 E2:E3 E4:F5 E6:E8 E10:E12 E14:E18 E20:E22 E23:F23 E24:E29 E34:E36 E38:E40 E42:E45 E47:E51 E55:E59 E61:E63 E65:E66 G65:G66 E68:E74 E76:E80 E82:E84 E86:E87 E92:E96 E98:E102 E104 E106:E108 E111 E113 E117:F1048576 E9:F9">
     <cfRule type="cellIs" dxfId="134" priority="256" operator="equal">
@@ -7465,30 +7800,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:F13">
-    <cfRule type="cellIs" dxfId="131" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="80" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="81" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="80" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:F19">
-    <cfRule type="cellIs" dxfId="129" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="75" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="128" priority="76" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="75" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:F33">
     <cfRule type="cellIs" dxfId="127" priority="69" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="70" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="125" priority="71" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="70" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:F37">
@@ -7503,24 +7838,24 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:F41">
-    <cfRule type="cellIs" dxfId="121" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="61" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="120" priority="62" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="63" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46:F46">
-    <cfRule type="cellIs" dxfId="118" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="58" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="59" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="60" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="60" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7536,11 +7871,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E60:F60">
-    <cfRule type="cellIs" dxfId="112" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="53" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="54" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="53" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64:F64">
@@ -7566,11 +7901,11 @@
     <cfRule type="cellIs" dxfId="105" priority="39" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="40" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="41" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="40" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E81:F81">
@@ -7593,35 +7928,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E88:F91">
-    <cfRule type="cellIs" dxfId="97" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="28" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="29" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="30" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="30" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:F97">
-    <cfRule type="cellIs" dxfId="94" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="25" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="93" priority="26" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="27" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E103:F103">
-    <cfRule type="cellIs" dxfId="91" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="22" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="90" priority="23" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="24" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7634,14 +7969,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E109:F110">
-    <cfRule type="cellIs" dxfId="86" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="11" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="12" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="13" operator="equal">
       <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="12" operator="equal">
-      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E112:F112">
@@ -7857,19 +8192,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:H36">
-    <cfRule type="cellIs" dxfId="39" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="129" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="130" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="129" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:H40">
-    <cfRule type="cellIs" dxfId="37" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="126" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="127" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="126" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42:H42 G44:H44">
@@ -7925,19 +8260,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G92:H96">
-    <cfRule type="cellIs" dxfId="23" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="99" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="100" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="99" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G98:H102">
-    <cfRule type="cellIs" dxfId="21" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="96" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="97" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="96" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G104:H104">
@@ -7951,19 +8286,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G111:H111">
-    <cfRule type="cellIs" dxfId="17" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="87" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="88" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="87" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G113:H113">
-    <cfRule type="cellIs" dxfId="15" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="84" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="85" operator="equal">
       <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="84" operator="equal">
-      <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H3 H65:H66">
@@ -8054,14 +8389,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8EC31C3-06F5-47FC-9863-DA5074DD945B}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="1" max="1" width="44.5" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="55.5703125" customWidth="1"/>
+    <col min="3" max="3" width="55.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -8075,166 +8410,166 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="105.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
+    <row r="2" spans="1:4" ht="81" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="157" t="s">
+      <c r="C2" s="35" t="s">
         <v>126</v>
       </c>
       <c r="D2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="157" t="s">
+    <row r="3" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="157" t="s">
+      <c r="C3" s="35" t="s">
         <v>127</v>
       </c>
       <c r="D3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="157" t="s">
+    <row r="4" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="35" t="s">
         <v>128</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
+    <row r="5" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A5" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="157" t="s">
+      <c r="C5" s="35" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A6" s="157" t="s">
+    <row r="6" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="157" t="s">
+      <c r="B6" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="157" t="s">
+      <c r="C6" s="35" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A7" s="157" t="s">
+    <row r="7" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="35" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A8" s="157" t="s">
+    <row r="8" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="157" t="s">
+      <c r="B8" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="157" t="s">
+      <c r="C8" s="35" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A9" s="157" t="s">
+    <row r="9" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A9" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="157" t="s">
+      <c r="B9" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="157" t="s">
+      <c r="C9" s="35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="240" x14ac:dyDescent="0.25">
-      <c r="A10" s="157" t="s">
+    <row r="10" spans="1:4" ht="160" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="157" t="s">
+      <c r="C10" s="35" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A11" s="157" t="s">
+    <row r="11" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="A11" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="157" t="s">
+      <c r="C11" s="35" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="A12" s="157" t="s">
+    <row r="12" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="157" t="s">
+      <c r="C12" s="35" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="157" t="s">
+    <row r="13" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A13" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="157" t="s">
+      <c r="B13" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="157" t="s">
+      <c r="C13" s="35" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A14" s="157" t="s">
+    <row r="14" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="157" t="s">
+      <c r="B14" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="157" t="s">
+      <c r="C14" s="35" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A15" s="157" t="s">
+    <row r="15" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="157" t="s">
+      <c r="B15" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="157" t="s">
+      <c r="C15" s="35" t="s">
         <v>143</v>
       </c>
     </row>
@@ -8247,49 +8582,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Q3"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="11.5" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
-      <c r="C2" s="156" t="s">
+      <c r="C2" s="159" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="156"/>
-    </row>
-    <row r="3" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+    </row>
+    <row r="3" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="156"/>
-      <c r="O3" s="156"/>
-      <c r="P3" s="156"/>
-      <c r="Q3" s="156"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="159"/>
+      <c r="O3" s="159"/>
+      <c r="P3" s="159"/>
+      <c r="Q3" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8304,31 +8639,1484 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C605E8-B378-924E-8C25-13AA18AF4394}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="90" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="72.6640625" customWidth="1"/>
+    <col min="5" max="5" width="95.5" style="166" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="168" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="169"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="166" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="166" t="str">
+        <f>+_xlfn.CONCAT(A2,B2)</f>
+        <v xml:space="preserve">1.1 ¿Está claramente definido el objetivo general del programa/proyecto? (Por ejemplo, ¿identifica la propuesta cómo contribuye la intervención a los resultados de la OIT, tal y como se establece en P&amp;B y el DWCP?)La intervención especifica su contribución a las prioridades a largo plazo de la OIT, los resultados y los resultados del DWCP, incluidos los CPO pertinentes. </v>
+      </c>
+      <c r="F2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="166" t="str">
+        <f t="shared" ref="E3:E66" si="0">+_xlfn.CONCAT(A3,B3)</f>
+        <v>1.1 ¿Está claramente definido el objetivo general del programa/proyecto? (Por ejemplo, ¿identifica la propuesta cómo contribuye la intervención a los resultados de la OIT, tal y como se establece en P&amp;B y el DWCP?)El nivel de ambición y visibilidad con respecto a la inclusión de la discapacidad en la propuesta está a la par con la etiqueta de inclusión de la discapacidad de los CPO correspondientes.</v>
+      </c>
+      <c r="F3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.1 ¿Está claramente definido el objetivo general del programa/proyecto? (Por ejemplo, ¿identifica la propuesta cómo contribuye la intervención a los resultados de la OIT, tal y como se establece en P&amp;B y el DWCP?)El nivel de ambición y visibilidad con respecto a la igualdad de género en la propuesta está a la par con el marcador de igualdad de género de los CPO correspondientes.</v>
+      </c>
+      <c r="F4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="171" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.2 ¿Identifica el proyecto los ODS pertinentes, el marco de cooperación de las Naciones Unidas, los marcos nacionales de los ODS y otros marcos de cooperación, incluidos los planes nacionales de desarrollo, y se ajusta a ellos?La propuesta explica cómo el proyecto encaja en el marco más amplio de la ayuda al desarrollo del país, incluidos los planes nacionales de desarrollo.</v>
+      </c>
+      <c r="F5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="172" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1.2 ¿Iyntifica con cooperación ODS pertindetes, con de ár cooperación ár las Naciones Unidas, que des responsable ár que ODS y otros marcos ár cooperación, incluidos los planes nacionales de desarrollo, y se ajusta N conque?La propuesta es coherente con el marco de cooperación de las Naciones Unidas y contribuye a las áreas específicas de las que es responsable la OIT. </v>
+      </c>
+      <c r="F6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="173" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.2 ¿Isonntifica indicadores ODS pertinlostes, indicadores que in cooperación in las Naciones Unidas, vinculados ques los in vinculados ODS y otros marcos in cooperación, incluidos los planes nacionales de desarrollo, y se ajusta c indicadoresvinculados?La propuesta identifica los indicadores pertinentes de los ODS que son coherentes con los indicadores de los ODS vinculados a los CPO pertinentes.</v>
+      </c>
+      <c r="F7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.3 ¿Es la intervención propuesta pertinente para abordar el problema identificado y responde a todos los aspectos planteados en los análisis del problema y de las partes interesadas?Se ha formulado una descripción del problema mediante un análisis de la situación (estudio de referencia u otras pruebas).</v>
+      </c>
+      <c r="F8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.3 ¿Es la intervención propuesta pertinente para abordar el problema identificado y responde a todos los aspectos planteados en los análisis del problema y de las partes interesadas?Se explican las causas del problema.</v>
+      </c>
+      <c r="F9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="116" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1.3 ¿Es la intervención propuesta pertinente para abordar el problema identificado y responde a todos los aspectos planteados en los análisis del problema y de las partes interesadas?Se ha identificado el grupo de población/los beneficiarios finales afectados por el problema y la propuesta, en lo que respecta al género, hace referencia a los roles de género existentes, la división del trabajo, las oportunidades y las limitaciones de las mujeres y los hombres para acceder a los recursos y controlarlos. En lo que respecta a las personas con discapacidad, se han identificado las estadísticas/datos pertinentes, así como sus derechos, necesidades y prioridades. </v>
+      </c>
+      <c r="F10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.3 ¿Es la intervención propuesta pertinente para abordar el problema identificado y responde a todos los aspectos planteados en los análisis del problema y de las partes interesadas?Se han identificado las partes interesadas relacionadas con el problema y la solución propuesta, junto con sus respectivas limitaciones e intereses en contribuir a la solución propuesta para el problema. El análisis de las partes interesadas se llevó a cabo de manera sensible al género e incluyó, cuando fue pertinente, a las organizaciones de personas con discapacidad.</v>
+      </c>
+      <c r="F11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="56.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.3 ¿Es la intervención propuesta pertinente para abordar el problema identificado y responde a todos los aspectos planteados en los análisis del problema y de las partes interesadas?El proyecto incluye una consulta significativa con todas las partes interesadas afectadas, especialmente los grupos marginados y excluidos. Garantiza una participación equitativa y evita los efectos discriminatorios sobre los grupos marginados, incluidas las personas con discapacidad, las comunidades indígenas, etc.</v>
+      </c>
+      <c r="F12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="171" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.4 ¿Hace hincapié la propuesta en la ventaja comparativa de la OIT para llevar a cabo este proyecto y en sus puntos fuertes en términos de experiencias previas en el ámbito técnico?La propuesta destaca la identidad normativa y tripartita de la OIT, su capacidad y su valor añadido para llevar a cabo el proyecto.</v>
+      </c>
+      <c r="F13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="171" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.4 ¿Hace hincapié la propuesta en la ventaja comparativa de la OIT para llevar a cabo este proyecto y en sus puntos fuertes en términos de experiencias previas en el ámbito técnico?Se destaca la presencia de la OIT en el país en cuestión, así como la cartera de proyectos pasados y en curso.</v>
+      </c>
+      <c r="F14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="171" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.4 ¿Hace hincapié la propuesta en la ventaja comparativa de la OIT para llevar a cabo este proyecto y en sus puntos fuertes en términos de experiencias previas en el ámbito técnico?La propuesta presenta experiencias previas, lecciones aprendidas de evaluaciones pertinentes (evaluaciones de proyectos, programas por país o estrategias,véase www.ilo.org/ievaldiscovery) y explica cómo estas han influido en la estrategia del proyecto.</v>
+      </c>
+      <c r="F15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?El proyecto ha tenido en cuenta las necesidades y preocupaciones de las personas con discapacidad.
+Orientación disponible:«Guía práctica» n.º 18: Inclusión de las personas con discapacidad.https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20on%20inclusion%20of%20people%20with%20disabilities%2010%20.pdf</v>
+      </c>
+      <c r="F16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="84.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="89" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?La propuesta integra los convenios y recomendaciones pertinentes de la OIT en la estrategia, los indicadores y los objetivos del proyecto, promoviendo la ratificación, la aplicación y el conocimiento de las normas laborales. Se incluyen referencias a NORMLEX u otras fuentes jurídicas de la OIT para reforzar la armonización con las normas internacionales del trabajo
+(véase NORMLEX: https://www.ilo.org/dyn/normlex/en/f?p=NORMLEXPUB:1:0::NO).
+</v>
+      </c>
+      <c r="F17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="112"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?En la propuesta se hace referencia a los informes de los organismos de supervisión específicos del país y a las normas internacionales del trabajo pertinentes en la justificación del proyecto y la estrategia de ejecución.</v>
+      </c>
+      <c r="F18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="112"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?La propuesta garantiza el cumplimiento de las normas laborales de la OIT, incluidos los salarios justos, las condiciones de trabajo seguras y los derechos fundamentales de los trabajadores. Si se contrata a trabajadores directamente o a través de terceros, se aplican medidas de protección para prevenir la explotación, el trabajo infantil y el trabajo forzoso.</v>
+      </c>
+      <c r="F19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="89" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="109"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?La propuesta da prioridad a la sostenibilidad ambiental, integrando medidas de seguridad y protección en la planificación del proyecto, en particular en lo que respecta a la infraestructura, la construcción y la gestión de materiales peligrosos. Evalúa los posibles impactos en la biodiversidad, los ecosistemas y las áreas protegidas, garantizando que las actividades agrícolas, forestales, ganaderas y pesqueras se realicen de manera sostenible. Además, se aplican estrategias de reducción del riesgo de desastres en las zonas propensas a los peligros, junto con medidas para promover la producción sostenible y minimizar la contaminación ambiental.</v>
+      </c>
+      <c r="F20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1.5 ¿Refleja la propuesta las áreas transversales de la OIT de manera pertinente e integrada?Siempre que es posible, la propuesta promueve y destaca el uso de un enfoque transformador en materia de género.
+Orientación disponible: «Guía práctica» n.º 15: Incorporación de la perspectiva de género https://intranet.ilo.org/en-us/PARDEV/Documents/Gender%20H2G%20June%202022.pdf </v>
+      </c>
+      <c r="F21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.1 ¿Han participado los socios tripartitos y otras partes interesadas clave en el diseño del proyecto?La propuesta describe el proceso de participación de los constituyentes y otras partes interesadas en el diseño del proyecto, y hace referencia específica a su papel en el seguimiento y la ejecución del proyecto.</v>
+      </c>
+      <c r="F22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.1 ¿Han participado los socios tripartitos y otras partes interesadas clave en el diseño del proyecto?Las partes interesadas clave se identifican claramente y se presentan en relación con su vínculo con los beneficiarios finales y su papel en relación con el problema identificado y la solución propuesta.</v>
+      </c>
+      <c r="F23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.1 ¿Han participado los socios tripartitos y otras partes interesadas clave en el diseño del proyecto?Se ha consultado a especialistas de ACT/EMP y ACTRAV.</v>
+      </c>
+      <c r="F24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="63"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.2 ¿Existe apropiación del proyecto por parte de los grupos destinatarios y otras partes interesadas pertinentes, y se presenta de manera convincente en la propuesta?La propuesta describe las consultas y los acuerdos alcanzados con los socios y su disposición a contribuir al logro de los resultados del proyecto (intención de apoyar la reforma, tiempo del personal pertinente para la capacitación y la aplicación de los cambios, etc.).</v>
+      </c>
+      <c r="F25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.2 ¿Existe apropiación del proyecto por parte de los grupos destinatarios y otras partes interesadas pertinentes, y se presenta de manera convincente en la propuesta?Cada socio ha aceptado los objetivos y metas del proyecto (según corresponda), el marco de desempeño y las obligaciones y responsabilidades correspondientes.</v>
+      </c>
+      <c r="F26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.2 ¿Existe apropiación del proyecto por parte de los grupos destinatarios y otras partes interesadas pertinentes, y se presenta de manera convincente en la propuesta?La propuesta explica la estrategia mediante la cual se fomentará y garantizará de forma continua la apropiación por parte de las partes interesadas.</v>
+      </c>
+      <c r="F27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="160" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="161"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.3 ¿Establece la propuesta un enfoque claro y holístico para el desarrollo de capacidades basado en una evaluación de las capacidades de los socios clave en la estrategia de resultados?
+Orientación disponible: Guía práctica n.º 12: Desarrollo de capacidades en la cooperación al desarrollo https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20on%20capacity%20development%20in%20development%20cooperation%203.pdf
+Orientación disponible: Guía práctica n.º 11: Evaluación de capacidades https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20on%20capacity%20assessment%20for%20development%20cooperation%202.pdf
+Se ha realizado o se prevé realizar una evaluación de la capacidad de los grupos destinatarios y sus conclusiones se mencionan explícitamente en la propuesta y se integran en el diseño del proyecto.</v>
+      </c>
+      <c r="F28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="163" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="164"/>
+      <c r="D29" s="165"/>
+      <c r="E29" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.3 ¿Establece la propuesta un enfoque claro y holístico para el desarrollo de capacidades basado en una evaluación de las capacidades de los socios clave en la estrategia de resultados?
+Orientación disponible: Guía práctica n.º 12: Desarrollo de capacidades en la cooperación al desarrollo https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20on%20capacity%20development%20in%20development%20cooperation%203.pdf
+Orientación disponible: Guía práctica n.º 11: Evaluación de capacidades https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20on%20capacity%20assessment%20for%20development%20cooperation%202.pdf
+La propuesta establece claramente su enfoque del desarrollo de capacidades, abordando tanto las capacidades individuales (técnicas) como las organizativas, así como el entorno propicio (político) necesario para lograr resultados.</v>
+      </c>
+      <c r="F29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.4 ¿Podrán los beneficiarios directos, por ejemplo, los socios o organismos nacionales, garantizar la sostenibilidad de los resultados en beneficio de los beneficiarios finales una vez finalizado el proyecto?De la propuesta se desprende claramente que los constituyentes y/u otras partes interesadas pertinentes han demostrado un gran interés en contribuir a la obtención de resultados tras la finalización del proyecto.</v>
+      </c>
+      <c r="F30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2.4 ¿Podrán los beneficiarios directos, por ejemplo, los socios o organismos nacionales, garantizar la sostenibilidad de los resultados en beneficio de los beneficiarios finales una vez finalizado el proyecto?La propuesta incluye planes para garantizar la sostenibilidad o los resultados tras la finalización del proyecto, por ejemplo, la formación de formadores, las asociaciones con actores locales, etc. </v>
+      </c>
+      <c r="F31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2.4 ¿Podrán los beneficiarios directos, por ejemplo, los socios o organismos nacionales, garantizar la sostenibilidad de los resultados en beneficio de los beneficiarios finales una vez finalizado el proyecto?En la fase de prueba, la propuesta identifica las condiciones previas necesarias para ampliar el enfoque y presenta el enfoque para demostrar objetivamente el éxito del mismo. </v>
+      </c>
+      <c r="F32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.4 ¿Podrán los beneficiarios directos, por ejemplo, los socios o organismos nacionales, garantizar la sostenibilidad de los resultados en beneficio de los beneficiarios finales una vez finalizado el proyecto?La propuesta hace plausible que los recursos necesarios (humanos y financieros) estarán disponibles una vez finalizado el proyecto.</v>
+      </c>
+      <c r="F33" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>2.4 ¿Podrán los beneficiarios directos, por ejemplo, los socios o organismos nacionales, garantizar la sostenibilidad de los resultados en beneficio de los beneficiarios finales una vez finalizado el proyecto?El proyecto incluye una estrategia de salida que establece planes para la transferencia de responsabilidades y las correspondientes intervenciones de desarrollo de capacidades, con el fin de garantizar que los socios nacionales sigan manteniendo los resultados del proyecto.</v>
+      </c>
+      <c r="F34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.1 ¿Se expresa claramente y se expone de forma explícita la teoría del cambio (por ejemplo, la expectativa de cómo se producirá realmente el cambio) de manera que resulte plausible para los no especialistas, en la narrativa y/o en un gráfico? Las relaciones causales, los mecanismos de cambio y las hipótesis entre los productos y los resultados, así como entre los resultados y el impacto, se explican de forma clara y convincente. El peso de la explicación recae en el logro de los resultados (más que en la realización de las actividades y la consecución de los productos).</v>
+      </c>
+      <c r="F35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.1 ¿Se expresa claramente y se expone de forma explícita la teoría del cambio (por ejemplo, la expectativa de cómo se producirá realmente el cambio) de manera que resulte plausible para los no especialistas, en la narrativa y/o en un gráfico? Los productos parecen suficientes para el probable logro de los resultados. La contribución esperada de los resultados al impacto también es clara.</v>
+      </c>
+      <c r="F36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.1 ¿Se expresa claramente y se expone de forma explícita la teoría del cambio (por ejemplo, la expectativa de cómo se producirá realmente el cambio) de manera que resulte plausible para los no especialistas, en la narrativa y/o en un gráfico? De la teoría del cambio se desprende claramente qué actores se beneficiarán del desarrollo de capacidades y cómo se espera que este conduzca a resultados tales como un mejor desempeño o un cambio de comportamiento, etc.</v>
+      </c>
+      <c r="F37" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.1 ¿Se expresa claramente y se expone de forma explícita la teoría del cambio (por ejemplo, la expectativa de cómo se producirá realmente el cambio) de manera que resulte plausible para los no especialistas, en la narrativa y/o en un gráfico? Se identifican los supuestos clave, incluidos los resultados de intervenciones pasadas, en curso o previstas (incluidas las de otros actores, según proceda).</v>
+      </c>
+      <c r="F38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.1 ¿Se expresa claramente y se expone de forma explícita la teoría del cambio (por ejemplo, la expectativa de cómo se producirá realmente el cambio) de manera que resulte plausible para los no especialistas, en la narrativa y/o en un gráfico? Las experiencias anteriores (otros proyectos o regiones) recopiladas a partir de evaluaciones o revisiones se citan como prueba para respaldar la relación causal prevista entre los productos, los resultados y el objetivo/impacto de desarrollo previsto, incluidas las lecciones aprendidas de evaluaciones anteriores.</v>
+      </c>
+      <c r="F39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="102"/>
+      <c r="D40" s="102"/>
+      <c r="E40" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.2 ¿Las formulaciones de los resultados reflejan las situaciones concretas que se pretenden alcanzar? Se utiliza un «lenguaje de cambio» en lugar de expresiones de «lenguaje de acción» como «a través de esto y aquello» o «haciendo esto y aquello», que se evitan. (Véase el Manual de gestión basada en los resultados del GNUD, https://unsdg.un.org/resources/unsdg-results-based-management-handbook</v>
+      </c>
+      <c r="F40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.2 ¿Las formulaciones de los resultados reflejan las situaciones concretas que se pretenden alcanzar? Los resultados (objetivos inmediatos) establecen claramente la situación final que se pretende alcanzar, las condiciones en las que se observará el desempeño y el estándar que se debe cumplir para llegar al resultado deseado. Las formulaciones de los resultados son específicas, medibles, alcanzables, relevantes y con plazos determinados.</v>
+      </c>
+      <c r="F41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.2 ¿Las formulaciones de los resultados reflejan las situaciones concretas que se pretenden alcanzar? Las formulaciones de los productos se refieren al resultado de las actividades más que a las actividades en sí mismas.</v>
+      </c>
+      <c r="F42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="171" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.3 ¿Se han incorporado la igualdad de género y la inclusión de la discapacidad en el marco lógico del proyecto?La igualdad de género se refleja en el nivel de los resultados y/o productos.</v>
+      </c>
+      <c r="F43" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="171" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="97"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.3 ¿Se han incorporado la igualdad de género y la inclusión de la discapacidad en el marco lógico del proyecto?La inclusión de las personas con discapacidad se refleja en el nivel de los resultados y/o productos.</v>
+      </c>
+      <c r="F44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfLa propuesta contiene un resumen narrativo/análisis de los riesgos.</v>
+      </c>
+      <c r="F45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="56.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="98" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfLa propuesta evalúa y mitiga los riesgos de explotación y abuso sexuales (EAS), incluidos los riesgos derivados de la afluencia de trabajadores, los cambios en las dinámicas de poder o una mayor exposición a entornos inseguros. Se han establecido mecanismos para prevenir la EAS, entre los que se incluyen la capacitación del personal, canales de denuncia seguros y una respuesta centrada en las víctimas.</v>
+      </c>
+      <c r="F46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="100"/>
+      <c r="E47" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfLa propuesta identifica y mitiga los riesgos para la salud y la seguridad de la comunidad, incluidos la contaminación atmosférica, los peligros del tráfico y la exposición a materiales peligrosos. Por ejemplo, si el proyecto cuenta con personal de seguridad, se han establecido medidas para prevenir daños a las comunidades y garantizar una participación responsable.</v>
+      </c>
+      <c r="F47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="34.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="99"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfSe mencionan/evalúan los riesgos de incumplimiento relacionados con las normas laborales y las observaciones de los organismos de supervisión.</v>
+      </c>
+      <c r="F48" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfPara los proyectos con un presupuesto superior a 1 millón de dólares estadounidenses, se ha rellenado la última versión del registro de riesgos y se ha adjuntado a la propuesta.</v>
+      </c>
+      <c r="F49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfLos riesgos identificados parecen relevantes y son lo suficientemente específicos como para ser significativos.</v>
+      </c>
+      <c r="F50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.4 ¿Se han evaluado los niveles de riesgo y se han propuesto medidas de mitigación, cuando procede?
+Orientación disponible: Guía práctica n.º 1: Identificación y gestión de riesgos. https://intranet.ilo.org/en-us/PARDEV/Documents/How%20to%20guide%20Analysing%20and%20responding%20to%20risk%20in%20project%20design.pdfSe proponen medidas pertinentes para abordar y supervisar los riesgos de nivel medio y alto.</v>
+      </c>
+      <c r="F51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="88.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.5 ¿Se han establecido mecanismos adecuados de seguimiento y evaluación?La sección de seguimiento y evaluación de la propuesta describe el sistema de seguimiento y evaluación previsto para recopilar la información de seguimiento necesaria de forma precisa y oportuna, de manera que se justifiquen los recursos necesarios. Incluye una revisión de la evaluabilidad (obligatoria para proyectos de más de 5 millones de dólares) y describe el tipo y la naturaleza de las evaluaciones que se llevarán a cabo según los requisitos de la política de evaluación de la OIT (enlace  más abajo). También tiene en cuenta la presentación de informes, la recopilación y el análisis de datos sobre la «rentabilidad».
+Consulte aquí:  https://www.ilo.org/eval/Evaluationpolicy/WCMS_571339/lang--en/index.htm</v>
+      </c>
+      <c r="F52" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="64.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="89"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3.5 ¿Se han establecido mecanismos adecuados de seguimiento y evaluación?Se describe el ciclo de retroalimentación de información sobre los avances en las decisiones de gestión del proyecto y se identifican claramente las necesidades de información para la presentación de informes sobre el desempeño. Se ha identificado al personal del proyecto responsable del seguimiento y la evaluación y se especifican las funciones y responsabilidades en materia de recopilación de datos, evaluación y presentación de informes. </v>
+      </c>
+      <c r="F53" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.5 ¿Se han establecido mecanismos adecuados de seguimiento y evaluación?El plan de seguimiento y evaluación se ha elaborado con necesidades de información bien identificadas para la presentación de informes sobre el desempeño. Los métodos de recopilación y análisis de datos sugeridos son técnicamente adecuados y viables. Especifica las funciones y responsabilidades en materia de seguimiento, evaluación y presentación de informes sobre los resultados.</v>
+      </c>
+      <c r="F54" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3.5 ¿Se han establecido mecanismos adecuados de seguimiento y evaluación?El plan de seguimiento y evaluación incluye indicadores SMART y sensibles al género, bases de referencia, objetivos e hitos (que también permiten la inclusión de las personas con discapacidad y/o de otros grupos vulnerables). Los indicadores miden los resultados previstos. Existe una base de referencia que describe la situación anterior a la intervención, lo que permite comparar los resultados. Los objetivos se calculan sumando la cantidad de cambio deseado con respecto a las bases de referencia. Los hitos se calculan dividiendo los objetivos en incrementos con plazos determinados. </v>
+      </c>
+      <c r="F55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="260" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.5 ¿Se han establecido mecanismos adecuados de seguimiento y evaluación?El presupuesto de seguimiento y evaluación se ajusta a las directrices de la OIT (enlace más abajo). El presupuesto de evaluación figura en una partida presupuestaria separada y es adecuado para el tamaño y la duración del proyecto (2 % del presupuesto total requerido según las directrices de la OIT). Lo mismo ocurre con el presupuesto de seguimiento (se recomienda el 3 % del presupuesto total del proyecto). Consulte aquí: https://www.ilo.org/eval/Evaluationpolicy/WCMS_571339/lang--en/index.htmTenga en cuenta que las cláusulas relacionadas con la evaluación pueden negociarse con los socios financieros. La opción 1 permite agrupar las evaluaciones para mejorar el aprendizaje organizativo y reducir la carga de la evaluación, y el calendario y el alcance se determinan en consulta con las partes interesadas, incluido el socio financiero. La opción 2 ofrece flexibilidad mediante contribuciones al Fondo Fiduciario de Evaluación de la OIT (IETF), ya sea asignando hasta el 1,5 % del presupuesto del proyecto durante la fase de diseño o transfiriendo los fondos de evaluación no utilizados después de las evaluaciones obligatorias. En ambos casos, los temas de las evaluaciones realizadas con estos fondos se acordarán con EVAL. 
+Haga clic aquí: https://iloprod.sharepoint.com/:b:/r/teams/EVAL-LIBRARY/Shared Documents/General/Management/Relations/PARDEV/Agreements with donors/ILO Evaluation Office_Evaluation clauses in agreements with funding partners (October 2024).pdf?csf=1&amp;web=1&amp;e=qR7Kfu</v>
+      </c>
+      <c r="F56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="171" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="88"/>
+      <c r="D57" s="88"/>
+      <c r="E57" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.6 ¿Se pueden lograr todos los resultados del proyecto (productos y resultados) dentro del plazo y el presupuesto establecidos?
+En caso de que haya un período inicial, la propuesta presenta claramente todas las actividades previstas que se llevarán a cabo durante este período y todos los resultados que se obtendrán al final del mismo. 
+El plazo es suficiente para alcanzar los resultados previstos, teniendo en cuenta también los retrasos previsibles en la puesta en marcha y los procedimientos administrativos dentro de la OIT.</v>
+      </c>
+      <c r="F57" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="171" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="89" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.6 ¿Se pueden lograr todos los resultados del proyecto (productos y resultados) dentro del plazo y el presupuesto establecidos?Hay pruebas claras de que el presupuesto se basa en un análisis de cada actividad prevista en el proyecto e incluye todos los recursos necesarios para su ejecución.</v>
+      </c>
+      <c r="F58" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="171" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="135" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="136"/>
+      <c r="D59" s="137"/>
+      <c r="E59" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3.6 ¿Se pueden lograr todos los resultados del proyecto (productos y resultados) dentro del plazo y el presupuesto establecidos?Cuando procede, el presupuesto incluye disposiciones para conocimientos especializados específicos (por ejemplo, inclusión de género o discapacidad), así como medios que promueven la inclusión (por ejemplo, accesibilidad de la información: interpretación en idiomas locales, lenguaje de señas, accesibilidad de los edificios, adaptaciones razonables, etc.). </v>
+      </c>
+      <c r="F59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B60" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.7 ¿Existen pruebas de que se ha tenido en cuenta la rentabilidad/relación calidad-precio al diseñar la estrategia del proyecto?En la propuesta se hace referencia a consideraciones de rentabilidad.</v>
+      </c>
+      <c r="F60" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>3.7 ¿Existen pruebas de que se ha tenido en cuenta la rentabilidad/relación calidad-precio al diseñar la estrategia del proyecto?La propuesta muestra que se ha encontrado el equilibrio más adecuado entre el gasto/ahorro de costos y el aumento/disminución de los beneficios.</v>
+      </c>
+      <c r="F61" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>4.1 ¿Son claras y suficientes las disposiciones de gestión? Los proyectos con resultados regionales o nacionales son gestionados por la oficina sobre el terreno más cercana a los beneficiarios. Los proyectos con una estructura de gestión centralizada propuesta en la sede central proporcionan una justificación basada en criterios de eficacia, rentabilidad, capacidad y eficiencia de la gestión.</v>
+      </c>
+      <c r="F62" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" s="50"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>4.1 ¿Son claras y suficientes las disposiciones de gestión? Las funciones y responsabilidades del personal que participa en el proyecto están claramente definidas. Existe una línea clara de rendición de cuentas y supervisión, y se identifica correctamente al funcionario responsable de la OIT.</v>
+      </c>
+      <c r="F63" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>4.1 ¿Son claras y suficientes las disposiciones de gestión? El apoyo de las unidades técnicas o administrativas de la sede y/o de los equipos de trabajo directos se ha previsto en el presupuesto según sea necesario.</v>
+      </c>
+      <c r="F64" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="86"/>
+      <c r="D65" s="87"/>
+      <c r="E65" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">4.1 ¿Son claras y suficientes las disposiciones de gestión? Las disposiciones de ejecución, incluidas la dotación de personal, las adquisiciones, los sistemas financieros y las autoridades, están claramente definidas. </v>
+      </c>
+      <c r="F65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="84"/>
+      <c r="D66" s="84"/>
+      <c r="E66" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>4.1 ¿Son claras y suficientes las disposiciones de gestión? Si el proyecto cuenta con la participación de contratistas, subcontratistas o proveedores externos, la propuesta menciona que estos se adhieren (o se adherirán) a los principios del trabajo decente y a condiciones de empleo justas. Existen mecanismos para que los trabajadores puedan presentar quejas y garantizar condiciones de trabajo seguras y equitativas.</v>
+      </c>
+      <c r="F66" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B67" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="166" t="str">
+        <f t="shared" ref="E67:E77" si="1">+_xlfn.CONCAT(A67,B67)</f>
+        <v>4.2 ¿Son claras las disposiciones de ejecución? Las responsabilidades y funciones de las instituciones y los socios participantes están claramente definidas. Se han establecido procedimientos de ejecución. La propuesta indica claramente por qué se han seleccionado determinadas instituciones.</v>
+      </c>
+      <c r="F67" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="50"/>
+      <c r="D68" s="50"/>
+      <c r="E68" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.2 ¿Son claras las disposiciones de ejecución? La propuesta indica si los socios participantes han aceptado las funciones y responsabilidades.</v>
+      </c>
+      <c r="F68" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.2 ¿Son claras las disposiciones de ejecución? Se ha llevado a cabo o se llevará a cabo una evaluación de la capacidad organizativa de los socios ejecutores y se hace referencia a ella en la propuesta.</v>
+      </c>
+      <c r="F69" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.2 ¿Son claras las disposiciones de ejecución? Si es necesario, se ha incluido en la propuesta un plan de desarrollo de la capacidad de los socios ejecutores, incluida la capacidad de respuesta en materia de género.</v>
+      </c>
+      <c r="F70" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" s="69"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.2 ¿Son claras las disposiciones de ejecución? La propuesta presenta pruebas suficientes de que los socios ejecutores garantizarán la ejecución eficaz del proyecto.</v>
+      </c>
+      <c r="F71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="174" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="70"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.3 ¿Incluye la propuesta una estrategia para la comunicación continua de los avances con las partes interesadas, incluidos los beneficiarios finales y directos?El proyecto describe cómo se comunicarán los datos y los resultados (incluidos los resultados de la evaluación) a las partes interesadas identificadas en el análisis de las partes interesadas y ha asignado los recursos adecuados (humanos y financieros) para llevarlo a cabo.</v>
+      </c>
+      <c r="F72" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.4 ¿Incluye o prevé la propuesta el desarrollo y la aplicación de una estrategia de comunicación presupuestada?La propuesta cuenta con una estrategia de comunicación para comunicar las actividades y los resultados desde una perspectiva de interés humano, con el público en general. Alternativamente, el proyecto incluye información sobre cómo y cuándo se desarrollará y aplicará una estrategia de comunicación.</v>
+      </c>
+      <c r="F73" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="67.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="64"/>
+      <c r="D74" s="64"/>
+      <c r="E74" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">4.4 ¿Incluye o prevé la propuesta el desarrollo y la aplicación de una estrategia de comunicación presupuestada?Se han asignado recursos adecuados (humanos y financieros) para el desarrollo y la implementación de una estrategia de comunicación. Los productos de comunicación son accesibles para las partes interesadas clave (por ejemplo, divulgación específica o formatos alternativos de información para personas con discapacidad). Véase: https://intranet.ilo.org/en-us/Pages/Disability-inclusion-and-accessibility-resources.aspx  </v>
+      </c>
+      <c r="F74" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="105.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="65"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>4.4 ¿Incluye o prevé la propuesta el desarrollo y la aplicación de una estrategia de comunicación presupuestada?Si el proyecto supera los 5 millones de dólares estadounidenses y se financia mediante acuerdos de colaboración público-privada o por la Comisión Europea, se ha completado una plantilla de estrategia de comunicación en colaboración con DCOMM (comms-help@ilo.org) y la oficina nacional correspondiente durante la fase inicial del proyecto. 
+(Disponible aquí: https://iloprod.sharepoint.com/sites/partnerships/SitePages/Communicating-results-and-good-practices-.aspx</v>
+      </c>
+      <c r="F75" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B76" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C76" s="55"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>5.1 ¿La propuesta sigue la plantilla?Se han completado todas las secciones y se han ordenado de acuerdo con los materiales de orientación.</v>
+      </c>
+      <c r="F76" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="55"/>
+      <c r="D77" s="55"/>
+      <c r="E77" s="166" t="str">
+        <f t="shared" si="1"/>
+        <v>5.2 ¿La propuesta está redactada de forma clara y concisa?La calidad de la redacción es alta; no hay detalles superfluos; las ideas centrales de cada sección están redactadas de forma clara y directa.</v>
+      </c>
+      <c r="F77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;1#&amp;"Calibri"&amp;10&amp;K000000</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">DOCID-739986004-48118</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">
-      <Url>https://intranet.ilo.org/collaborate/pardev/appraisals/_layouts/15/DocIdRedir.aspx?ID=DOCID-739986004-48118</Url>
-      <Description>DOCID-739986004-48118</Description>
-    </_dlc_DocIdUrl>
-    <PDDocumentStatus xmlns="48a19867-faf9-4f54-9178-1386f6a9b94c">Not Final</PDDocumentStatus>
-    <PDBudgetDocStatus xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">
-      <Value>776</Value>
-    </TaxCatchAll>
-    <PDProjectDCSymbol xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">HND/25/01/CAN</PDProjectDCSymbol>
-    <PDAppraisalID xmlns="http://schemas.microsoft.com/sharepoint/v3">4007</PDAppraisalID>
-    <PDAppraisalDocTypeTaxHTField0 xmlns="48a19867-faf9-4f54-9178-1386f6a9b94c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">proposal</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">4b7df3f8-8f10-44e1-ba99-786584f94717</TermId>
-        </TermInfo>
-      </Terms>
-    </PDAppraisalDocTypeTaxHTField0>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8582,53 +10370,30 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">DOCID-739986004-48118</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">
+      <Url>https://intranet.ilo.org/collaborate/pardev/appraisals/_layouts/15/DocIdRedir.aspx?ID=DOCID-739986004-48118</Url>
+      <Description>DOCID-739986004-48118</Description>
+    </_dlc_DocIdUrl>
+    <PDDocumentStatus xmlns="48a19867-faf9-4f54-9178-1386f6a9b94c">Not Final</PDDocumentStatus>
+    <PDBudgetDocStatus xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">
+      <Value>776</Value>
+    </TaxCatchAll>
+    <PDProjectDCSymbol xmlns="9db0404a-7623-4d3d-ab2f-ed8e1244f64e">HND/25/01/CAN</PDProjectDCSymbol>
+    <PDAppraisalID xmlns="http://schemas.microsoft.com/sharepoint/v3">4007</PDAppraisalID>
+    <PDAppraisalDocTypeTaxHTField0 xmlns="48a19867-faf9-4f54-9178-1386f6a9b94c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">proposal</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">4b7df3f8-8f10-44e1-ba99-786584f94717</TermId>
+        </TermInfo>
+      </Terms>
+    </PDAppraisalDocTypeTaxHTField0>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8641,13 +10406,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C6E2C2B-D93C-4D7A-819F-2B5FFE7A98F6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEA3FD7A-777D-4AF5-95D3-5BF9C2858DE0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9db0404a-7623-4d3d-ab2f-ed8e1244f64e"/>
-    <ds:schemaRef ds:uri="48a19867-faf9-4f54-9178-1386f6a9b94c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8674,9 +10435,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEA3FD7A-777D-4AF5-95D3-5BF9C2858DE0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C6E2C2B-D93C-4D7A-819F-2B5FFE7A98F6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9db0404a-7623-4d3d-ab2f-ed8e1244f64e"/>
+    <ds:schemaRef ds:uri="48a19867-faf9-4f54-9178-1386f6a9b94c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
